--- a/hotel_manager_forms/011_hostel_booking_form_light_coral_and_responsive--hotel_manager_forms.xlsx
+++ b/hotel_manager_forms/011_hostel_booking_form_light_coral_and_responsive--hotel_manager_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_7.1,_'label':_'australia'}</t>
+          <t>australia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 7.1, 'label': 'Australia'}</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_7.1,_'label':_'united_states'}</t>
+          <t>united_states</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 7.1, 'label': 'United States'}</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_7.2,_'label':_'canada'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 7.2, 'label': 'Canada'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_7.2,_'label':_'united_kingdom'}</t>
+          <t>united_kingdom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 7.2, 'label': 'United Kingdom'}</t>
+          <t>United Kingdom</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_7.3,_'label':_'germany'}</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 7.3, 'label': 'Germany'}</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_7.4,_'label':_'france'}</t>
+          <t>france</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 7.4, 'label': 'France'}</t>
+          <t>France</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_8.1,_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 8.1, 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8.1,_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8.1, 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_8.2,_'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 8.2, 'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_8.2,_'label':_'german'}</t>
+          <t>german</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 8.2, 'label': 'German'}</t>
+          <t>German</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_8.3,_'label':_'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 8.3, 'label': 'Chinese'}</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_8.4,_'label':_'japanese'}</t>
+          <t>japanese</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 8.4, 'label': 'Japanese'}</t>
+          <t>Japanese</t>
         </is>
       </c>
     </row>
